--- a/site-from-checkpoint/public_html/downloads/later-second-term-trump-admin-media-deception.xlsx
+++ b/site-from-checkpoint/public_html/downloads/later-second-term-trump-admin-media-deception.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Later Second Term Era" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Later Second Term Era" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Later Second Term Era'!$A$1:$L$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Later Second Term Era'!$A$1:$L$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -7190,8 +7190,323 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Said: “we cut the deficit by $1.7 trillion, the largest reduction in debt in American history.”
+Began: Jan 26, 2023 | Ended: repeated</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>https://home.treasury.gov/news/press-releases/jy1043</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Joe Biden (D), White House remarks</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>repeated / never corrected</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>deficit / debt conflation</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>misleading</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Primary record: Treasury: the FY2022 deficit fell $1.4 trillion, but borrowing from the public rose $2.0 trillion to $24.3 trillion. The debt was not reduced.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Rated misleading</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>https://bidenwhitehouse.archives.gov/briefing-room/speeches-remarks/2023/01/26/remarks-by-president-biden-on-economic-progress-since-taking-office/</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Official record</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>Never corrected — fact-checked only</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Said: “for the first time in 10 years, seniors are getting an increase in their Social Security checks” and “We cut the federal debt in half.”
+Began: Nov 2022 | Ended: never corrected</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnn.com/2022/11/05/politics/fact-check-biden-midterms-2022</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Joe Biden (D), midterm campaign remarks</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>repeated / never corrected</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>false claim</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Primary record: SSA cost-of-living increases were paid in 2012–2014 and 2016–2021. Treasury: borrowing from the public rose $2.0 trillion in FY2022; debt was not cut in half.</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Proven false</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ssa.gov/oact/cola/colaseries.html</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Official record</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>Never corrected — fact-checked only</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Said: “It was 9% when I came to office, 9%.”
+Began: May 2024 | Ended: never corrected</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.factcheck.org/2024/05/factchecking-biden-on-inflation-other-claims/</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Joe Biden (D), interview remarks</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>repeated / never corrected</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>wrong number</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Primary record: BLS: 12-month CPI inflation was 1.4% in January 2021; it peaked at 9.1% in June 2022, under Biden.</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Proven false</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bls.gov/opub/ted/2022/consumer-prices-up-7-7-percent-over-year-ended-october-2022.htm</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Official record</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>Never corrected — fact-checked only</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Said: “Two years ago this week, 18 million people were out of work ... Now that number is under 1.6 million.”
+Began: Jan 2023 | Ended: never corrected</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.factcheck.org/2023/01/bidens-misleading-unemployment-statistic/</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Joe Biden (D), U.S. Conference of Mayors remarks</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>repeated / never corrected</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>apples-to-oranges statistic</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>misleading</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Primary record: BLS: about 10.2 million unemployed in January 2021 and 5.7 million in December 2022. The 18 million and 1.6 million figures were unemployment-benefit recipients, not the unemployed.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Rated misleading</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bls.gov/news.release/empsit.t15.htm</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Official record</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>Never corrected — fact-checked only</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Took credit for the drop in violent crime, including the 2024 decline that came before he took office.
+Began: 2025 | Ended: repeated</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fbi.gov/news/stories/violent-crime-falls-at-historic-rate-new-fbi-data-show</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Kash Patel, FBI Director (R administration)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>repeated / never corrected</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>taking credit</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>misleading</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Primary record: FBI: violent crime fell 4.5% in 2024, before Patel became director, and 9.3% in 2025. The FBI's own page credits agencies working together.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Rated misleading</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fbi.gov/news/press-releases/fbi-releases-2024-reported-crimes-in-the-nation-statistics</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Official record</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Never corrected — fact-checked only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L111"/>
+  <autoFilter ref="A1:L116"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
@@ -7394,6 +7709,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId211"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
